--- a/templates/SolidPro_CC_Financials_Template.xlsx
+++ b/templates/SolidPro_CC_Financials_Template.xlsx
@@ -20,14 +20,14 @@
     <comment ref="A1" authorId="0">
       <text>
         <r>
-          <t>Required: Must exist in the master</t>
+          <t>Required: Must exist in the master. Every upload REPLACES all lines for every period it contains — include every cost centre for that period.</t>
         </r>
       </text>
     </comment>
     <comment ref="B1" authorId="0">
       <text>
         <r>
-          <t>Required: YYYY-MM</t>
+          <t>Required: YYYY-MM (or Oct-2026). One file may hold several periods, e.g. a month of actuals or a full-year budget.</t>
         </r>
       </text>
     </comment>
@@ -48,7 +48,7 @@
     <comment ref="E1" authorId="0">
       <text>
         <r>
-          <t>Required: Number, no currency symbols</t>
+          <t>Required: Number. Leave blank ONLY for budget-only (future) months; in a month with actuals enter 0, not blank. CC actuals per period must equal the trial balance.</t>
         </r>
       </text>
     </comment>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
   <si>
     <t>CC_Code</t>
   </si>
@@ -98,7 +98,7 @@
     <t>158400</t>
   </si>
   <si>
-    <t>SolidPro Cost Centre Portal — Budget &amp; Actuals (Phase 2) template</t>
+    <t>SolidPro Cost Centre Portal — Budget &amp; Actuals template</t>
   </si>
   <si>
     <t>Replace the example rows on the first sheet. Keep the header row unchanged. The upload is rejected as a whole if any row has an error.</t>
@@ -116,16 +116,19 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Must exist in the master</t>
-  </si>
-  <si>
-    <t>YYYY-MM</t>
+    <t>Must exist in the master. Every upload REPLACES all lines for every period it contains — include every cost centre for that period.</t>
+  </si>
+  <si>
+    <t>YYYY-MM (or Oct-2026). One file may hold several periods, e.g. a month of actuals or a full-year budget.</t>
   </si>
   <si>
     <t>GL group as mapped from the Tally export</t>
   </si>
   <si>
     <t>Number, no currency symbols</t>
+  </si>
+  <si>
+    <t>Number. Leave blank ONLY for budget-only (future) months; in a month with actuals enter 0, not blank. CC actuals per period must equal the trial balance.</t>
   </si>
 </sst>
 </file>
@@ -672,7 +675,7 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/templates/SolidPro_CC_Financials_Template.xlsx
+++ b/templates/SolidPro_CC_Financials_Template.xlsx
@@ -41,14 +41,14 @@
     <comment ref="D1" authorId="0">
       <text>
         <r>
-          <t>Required: Number, no currency symbols</t>
+          <t>Required: Number (commas, currency symbols and (brackets) for negatives are accepted). Required on every row — enter 0 if there is no budget.</t>
         </r>
       </text>
     </comment>
     <comment ref="E1" authorId="0">
       <text>
         <r>
-          <t>Required: Number. Leave blank ONLY for budget-only (future) months; in a month with actuals enter 0, not blank. CC actuals per period must equal the trial balance.</t>
+          <t>Required: Number. Leave blank ONLY for budget-only (future) months; in a month with actuals enter 0, not blank. CC actuals per period and entity must equal that entity's trial balance.</t>
         </r>
       </text>
     </comment>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
   <si>
     <t>CC_Code</t>
   </si>
@@ -74,6 +74,42 @@
     <t>Actual</t>
   </si>
   <si>
+    <t>SolidPro Cost Centre Portal — Budget &amp; Actuals template</t>
+  </si>
+  <si>
+    <t>Enter your rows on the "Financials" sheet under the header row. Keep the header row unchanged. The upload is rejected as a whole if any row has an error.</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>Rule</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Must exist in the master. Every upload REPLACES all lines for every period it contains — include every cost centre for that period.</t>
+  </si>
+  <si>
+    <t>YYYY-MM (or Oct-2026). One file may hold several periods, e.g. a month of actuals or a full-year budget.</t>
+  </si>
+  <si>
+    <t>GL group as mapped from the Tally export</t>
+  </si>
+  <si>
+    <t>Number (commas, currency symbols and (brackets) for negatives are accepted). Required on every row — enter 0 if there is no budget.</t>
+  </si>
+  <si>
+    <t>Number. Leave blank ONLY for budget-only (future) months; in a month with actuals enter 0, not blank. CC actuals per period and entity must equal that entity's trial balance.</t>
+  </si>
+  <si>
+    <t>Example rows (for illustration only — do not copy blindly)</t>
+  </si>
+  <si>
     <t>IN-ENG-101</t>
   </si>
   <si>
@@ -96,46 +132,13 @@
   </si>
   <si>
     <t>158400</t>
-  </si>
-  <si>
-    <t>SolidPro Cost Centre Portal — Budget &amp; Actuals template</t>
-  </si>
-  <si>
-    <t>Replace the example rows on the first sheet. Keep the header row unchanged. The upload is rejected as a whole if any row has an error.</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>Required</t>
-  </si>
-  <si>
-    <t>Rule</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Must exist in the master. Every upload REPLACES all lines for every period it contains — include every cost centre for that period.</t>
-  </si>
-  <si>
-    <t>YYYY-MM (or Oct-2026). One file may hold several periods, e.g. a month of actuals or a full-year budget.</t>
-  </si>
-  <si>
-    <t>GL group as mapped from the Tally export</t>
-  </si>
-  <si>
-    <t>Number, no currency symbols</t>
-  </si>
-  <si>
-    <t>Number. Leave blank ONLY for budget-only (future) months; in a month with actuals enter 0, not blank. CC actuals per period must equal the trial balance.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -155,6 +158,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF16469D"/>
     </font>
   </fonts>
   <fills count="3">
@@ -182,13 +189,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -528,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="16" style="1" customWidth="1"/>
@@ -549,40 +557,6 @@
       </c>
       <c r="E1" s="3" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -594,7 +568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -604,23 +578,23 @@
   <sheetData>
     <row r="1" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -628,10 +602,10 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -639,10 +613,10 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -650,10 +624,10 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -661,10 +635,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -672,10 +646,66 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
         <v>18</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" t="s">
         <v>23</v>
+      </c>
+      <c r="E14" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
